--- a/sample-data/stress/cmdb-export.xlsx
+++ b/sample-data/stress/cmdb-export.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookups" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Zephyr Logistics — CMDB Export (Q3)</t>
+          <t>Zephyr Logistics — CMDB Export (Q3) · extracted 2025-11-03 by svc-cmdb-sync</t>
         </is>
       </c>
     </row>
@@ -460,6 +461,21 @@
           <t>cpu_utilization_pct</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -487,7 +503,22 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>71</v>
+        <v>58.4</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>priya.nair@zephyr-logistics.example</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -511,7 +542,22 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>priya.nair@zephyr-logistics.example</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -537,64 +583,539 @@
       <c r="G6" t="n">
         <v>55</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>tom.becker@zephyr-logistics.example</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fleet-db-01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DC-South</t>
+          <t>PAY-DB-01.DCN.ZEPHYR.LOCAL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ubuntu 22.04</t>
+          <t>RHEL 7</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>1024</v>
+        <v>2048</v>
       </c>
       <c r="G7" t="n">
-        <v>62</v>
+        <v>44</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>tom.becker@zephyr-logistics.example</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rpt-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Windows Server 2012 R2</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" t="n">
+        <v>500</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>infra-team@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ord-api-legacy</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>RHEL 7</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>priya.nair@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pay-svc-00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Windows Server 2012</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>tom.becker@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mon-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CentOS 7</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>infra-team@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>file-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Windows Server 2016</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4096</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>infra-team@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>zl-as400</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IBM i 7.4</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>infra-team@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fleet-db-01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DC-South</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" t="n">
+        <v>64</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G14" t="n">
+        <v>62</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ana.silva@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>fleet-db-02</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Ubuntu 22.04</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D15" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E15" t="n">
         <v>64</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F15" t="n">
         <v>1024</v>
       </c>
-      <c r="G8" t="n">
-        <v>60</v>
+      <c r="G15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ana.silva@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>kafka-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RHEL 8</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ana.silva@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>kafka-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RHEL 8</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>32</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G17" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ana.silva@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fleet-ing-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16</v>
+      </c>
+      <c r="F18" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" t="n">
+        <v>76</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ana.silva@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>idp-02</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>80</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>infra-team@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D20">
+        <f>SUM(D4:D19)</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>SUM(E4:E19)</f>
+        <v/>
+      </c>
+      <c r="F20">
+        <f>SUM(F4:F19)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="B4:B13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -606,6 +1127,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>datacenter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DC-North</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Staging</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DC-South</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/sample-data/stress/cmdb-export.xlsx
+++ b/sample-data/stress/cmdb-export.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,103 +428,91 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hostname</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>datacenter</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>os</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>vcpu</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>memory_gb</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>disk_gb</t>
+          <t>Configured capacity</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>cpu_utilization_pct</t>
+          <t>Utilisation</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>environment</t>
+          <t>Lifecycle</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>Ownership</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ord-api-01</t>
+          <t>hostname</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DC-North</t>
+          <t>datacenter</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RHEL 9</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>32</v>
-      </c>
-      <c r="F4" t="n">
-        <v>200</v>
-      </c>
-      <c r="G4" t="n">
-        <v>58.4</v>
+          <t>os</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>vcpu</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>memory_gb</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>disk_gb</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>cpu_utilization_pct</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>In Service</t>
+          <t>status</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Prod</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>priya.nair@zephyr-logistics.example</t>
+          <t>owner</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ord-api-02</t>
+          <t>ord-api-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DC-North</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -542,7 +530,7 @@
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>71</v>
+        <v>58.4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -563,25 +551,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pay-svc-01</t>
+          <t>ord-api-02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Windows Server 2022</t>
+          <t>RHEL 9</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -595,32 +583,32 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>tom.becker@zephyr-logistics.example</t>
+          <t>priya.nair@zephyr-logistics.example</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAY-DB-01.DCN.ZEPHYR.LOCAL</t>
+          <t>pay-svc-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RHEL 7</t>
+          <t>Windows Server 2022</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>2048</v>
+        <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -641,25 +629,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rpt-01</t>
+          <t>PAY-DB-01.DCN.ZEPHYR.LOCAL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Windows Server 2012 R2</t>
+          <t>RHEL 7</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
-        <v>500</v>
+        <v>2048</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -673,19 +661,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>infra-team@zephyr-logistics.example</t>
+          <t>tom.becker@zephyr-logistics.example</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ord-api-legacy</t>
+          <t>rpt-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RHEL 7</t>
+          <t>Windows Server 2012 R2</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -695,11 +683,14 @@
         <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>200</v>
+        <v>500</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>In Service</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -709,29 +700,29 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>priya.nair@zephyr-logistics.example</t>
+          <t>infra-team@zephyr-logistics.example</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pay-svc-00</t>
+          <t>ord-api-legacy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Windows Server 2012</t>
+          <t>RHEL 7</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -745,36 +736,33 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>tom.becker@zephyr-logistics.example</t>
+          <t>priya.nair@zephyr-logistics.example</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mon-01</t>
+          <t>pay-svc-00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CentOS 7</t>
+          <t>Windows Server 2012</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>500</v>
-      </c>
-      <c r="G11" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>In Service</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -784,19 +772,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>infra-team@zephyr-logistics.example</t>
+          <t>tom.becker@zephyr-logistics.example</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>file-01</t>
+          <t>mon-01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Windows Server 2016</t>
+          <t>CentOS 7</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -806,10 +794,10 @@
         <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>4096</v>
+        <v>500</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -830,13 +818,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zl-as400</t>
+          <t>file-01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IBM i 7.4</t>
-        </is>
+          <t>Windows Server 2016</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4096</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -857,30 +857,13 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fleet-db-01</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DC-South</t>
+          <t>zl-as400</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ubuntu 22.04</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>16</v>
-      </c>
-      <c r="E14" t="n">
-        <v>64</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1024</v>
-      </c>
-      <c r="G14" t="n">
-        <v>62</v>
+          <t>IBM i 7.4</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -894,14 +877,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ana.silva@zephyr-logistics.example</t>
+          <t>infra-team@zephyr-logistics.example</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fleet-db-02</t>
+          <t>fleet-db-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DC-South</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -919,7 +907,7 @@
         <v>1024</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -940,25 +928,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kafka-01</t>
+          <t>fleet-db-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RHEL 8</t>
+          <t>Ubuntu 22.04</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="F16" t="n">
         <v>1024</v>
       </c>
       <c r="G16" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -979,7 +967,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kafka-02</t>
+          <t>kafka-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -997,7 +985,7 @@
         <v>1024</v>
       </c>
       <c r="G17" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1018,25 +1006,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fleet-ing-01</t>
+          <t>kafka-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ubuntu 22.04</t>
+          <t>RHEL 8</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
-        <v>100</v>
+        <v>1024</v>
       </c>
       <c r="G18" t="n">
-        <v>76</v>
+        <v>47.5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1057,7 +1045,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>idp-02</t>
+          <t>fleet-ing-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1066,16 +1054,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1089,33 +1077,75 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>infra-team@zephyr-logistics.example</t>
+          <t>ana.silva@zephyr-logistics.example</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>idp-02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>80</v>
+      </c>
+      <c r="G20" t="n">
+        <v>19</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>In Service</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Prod</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>infra-team@zephyr-logistics.example</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D20">
-        <f>SUM(D4:D19)</f>
+      <c r="D21">
+        <f>SUM(D5:D20)</f>
         <v/>
       </c>
-      <c r="E20">
-        <f>SUM(E4:E19)</f>
+      <c r="E21">
+        <f>SUM(E5:E20)</f>
         <v/>
       </c>
-      <c r="F20">
-        <f>SUM(F4:F19)</f>
+      <c r="F21">
+        <f>SUM(F5:F20)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="B4:B13"/>
+  <mergeCells count="5">
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="B5:B14"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
